--- a/bin/rfc_requestors_source.xlsx
+++ b/bin/rfc_requestors_source.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa-report\bin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA8B29F-FD72-4181-B0D3-DE2525CA3938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AE5C77-02F6-4EE7-9AEA-8CF863E6FBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{5E4D3CA5-720D-4A52-91D7-666BEAB78D01}"/>
+    <workbookView xWindow="1965" yWindow="2490" windowWidth="24960" windowHeight="11430" activeTab="5" xr2:uid="{5E4D3CA5-720D-4A52-91D7-666BEAB78D01}"/>
   </bookViews>
   <sheets>
     <sheet name="FY19" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="FY21" sheetId="16" r:id="rId3"/>
     <sheet name="FY22" sheetId="15" r:id="rId4"/>
     <sheet name="FY23" sheetId="18" r:id="rId5"/>
+    <sheet name="FY24" sheetId="19" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,10 +28,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="21">
   <si>
     <t>Agency</t>
   </si>
@@ -96,6 +97,12 @@
   <si>
     <t>Commercial Corporations</t>
   </si>
+  <si>
+    <t>SEC</t>
+  </si>
+  <si>
+    <t>DOD</t>
+  </si>
 </sst>
 </file>
 
@@ -133,18 +140,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6508426B-287A-4A7A-B704-706E8CAADF1A}"/>
+    <cellStyle name="Normal_FY24" xfId="2" xr:uid="{4905F50E-EA48-4FDB-AE80-E6F33AA13555}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -773,8 +783,16 @@
       <c r="I14"/>
       <c r="J14"/>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -1105,8 +1123,16 @@
       <c r="I14"/>
       <c r="J14"/>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -1437,8 +1463,16 @@
       <c r="I14"/>
       <c r="J14"/>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -1765,8 +1799,16 @@
       <c r="I14"/>
       <c r="J14"/>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -2097,8 +2139,274 @@
       <c r="I14"/>
       <c r="J14"/>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{500C48D0-F34B-4314-A79A-F65BFE6657A6}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" customWidth="1"/>
+    <col min="5" max="5" width="31.42578125" customWidth="1"/>
+    <col min="6" max="6" width="36.140625" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+    </row>
+    <row r="13" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+    </row>
+    <row r="14" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+    </row>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+    </row>
     <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>

--- a/bin/rfc_requestors_source.xlsx
+++ b/bin/rfc_requestors_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AE5C77-02F6-4EE7-9AEA-8CF863E6FBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3605C9-A440-4363-A9EB-782C14E5DB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1965" yWindow="2490" windowWidth="24960" windowHeight="11430" activeTab="5" xr2:uid="{5E4D3CA5-720D-4A52-91D7-666BEAB78D01}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{5E4D3CA5-720D-4A52-91D7-666BEAB78D01}"/>
   </bookViews>
   <sheets>
     <sheet name="FY19" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="FY22" sheetId="15" r:id="rId4"/>
     <sheet name="FY23" sheetId="18" r:id="rId5"/>
     <sheet name="FY24" sheetId="19" r:id="rId6"/>
+    <sheet name="FY25" sheetId="20" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,18 +29,23 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="22">
   <si>
     <t>Agency</t>
   </si>
@@ -83,25 +89,28 @@
     <t>USDA</t>
   </si>
   <si>
-    <t>Trade Associations</t>
-  </si>
-  <si>
-    <t>Interest Groups</t>
-  </si>
-  <si>
-    <t>Professional societies/associations</t>
-  </si>
-  <si>
     <t>Others</t>
-  </si>
-  <si>
-    <t>Commercial Corporations</t>
   </si>
   <si>
     <t>SEC</t>
   </si>
   <si>
     <t>DOD</t>
+  </si>
+  <si>
+    <t>DOT</t>
+  </si>
+  <si>
+    <t>Professional societies</t>
+  </si>
+  <si>
+    <t>Trade Associations</t>
+  </si>
+  <si>
+    <t>Commercial Corporations</t>
+  </si>
+  <si>
+    <t>Interest Groups</t>
   </si>
 </sst>
 </file>
@@ -140,21 +149,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6508426B-287A-4A7A-B704-706E8CAADF1A}"/>
     <cellStyle name="Normal_FY24" xfId="2" xr:uid="{4905F50E-EA48-4FDB-AE80-E6F33AA13555}"/>
+    <cellStyle name="Normal_FY25" xfId="3" xr:uid="{E3D1E807-28EA-4093-A773-5417F372921C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -484,19 +496,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
         <v>14</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -785,16 +797,20 @@
     </row>
     <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -820,19 +836,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
         <v>14</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1125,16 +1141,20 @@
     </row>
     <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1160,19 +1180,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
         <v>14</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1465,16 +1485,20 @@
     </row>
     <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1500,19 +1524,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
         <v>14</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1801,16 +1825,20 @@
     </row>
     <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1836,19 +1864,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
         <v>14</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2141,16 +2169,20 @@
     </row>
     <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2176,19 +2208,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
         <v>14</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2393,7 +2425,7 @@
     </row>
     <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C15" s="1">
         <v>1</v>
@@ -2401,14 +2433,291 @@
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{960BBE8C-7FC6-4D0A-BB79-489712134352}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" customWidth="1"/>
+    <col min="5" max="5" width="31.42578125" customWidth="1"/>
+    <col min="6" max="6" width="36.140625" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4">
+        <v>3</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4">
+        <v>6</v>
+      </c>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+    </row>
+    <row r="13" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2">
+        <v>4</v>
+      </c>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+    </row>
+    <row r="14" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>2</v>
+      </c>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+    </row>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
